--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run6/epoch_50/per_file_predictions_epoch_50.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run6/epoch_50/per_file_predictions_epoch_50.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="507">
   <si>
     <t>Filename</t>
   </si>
@@ -808,739 +808,733 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.9857,0.0018,0.0036,0.0007</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9768,0.0038,0.0054,0.0024</t>
+  </si>
+  <si>
+    <t>0.0005,0.0000,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.7819,0.0008,0.0006,0.2410</t>
+  </si>
+  <si>
+    <t>0.0164,0.0032,0.0004,0.9910</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9987,0.0000,0.0000,0.0016</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9979,0.0010,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.5259,0.0001,0.5833,0.0001</t>
+  </si>
+  <si>
+    <t>0.0025,0.0010,0.9954,0.0005</t>
+  </si>
+  <si>
+    <t>0.9222,0.0008,0.1043,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0010,0.9987,0.0002</t>
+  </si>
+  <si>
+    <t>0.9915,0.0004,0.0055,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9995,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.9993,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0450,0.9658,0.0017,0.0000</t>
+  </si>
+  <si>
+    <t>0.0016,0.9974,0.0017,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9805,0.0002,0.0113,0.0001</t>
+  </si>
+  <si>
+    <t>0.9737,0.0009,0.0121,0.0001</t>
+  </si>
+  <si>
+    <t>0.0013,0.0001,0.9985,0.0002</t>
+  </si>
+  <si>
+    <t>0.0102,0.0008,0.9845,0.0010</t>
+  </si>
+  <si>
+    <t>0.0457,0.0000,0.9736,0.0000</t>
+  </si>
+  <si>
+    <t>0.9850,0.0000,0.0321,0.0000</t>
+  </si>
+  <si>
+    <t>0.0052,0.0001,0.9931,0.0006</t>
+  </si>
+  <si>
+    <t>0.8578,0.1575,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.1228,0.1870,0.3565,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0014,0.9998,0.0240</t>
+  </si>
+  <si>
+    <t>0.0037,0.9949,0.0016,0.0003</t>
+  </si>
+  <si>
+    <t>0.9019,0.0008,0.0710,0.0018</t>
+  </si>
+  <si>
+    <t>0.0032,0.0036,0.9915,0.0287</t>
+  </si>
+  <si>
+    <t>0.2663,0.7467,0.0033,0.0002</t>
+  </si>
+  <si>
+    <t>0.0010,0.9949,0.0928,0.0002</t>
+  </si>
+  <si>
+    <t>0.0047,0.9604,0.0543,0.0016</t>
+  </si>
+  <si>
+    <t>0.0046,0.0002,0.9885,0.0017</t>
+  </si>
+  <si>
+    <t>0.0671,0.0248,0.8776,0.0015</t>
+  </si>
+  <si>
+    <t>0.0159,0.0002,0.9633,0.0066</t>
+  </si>
+  <si>
+    <t>0.0015,0.0012,0.9969,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9976,0.0060,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9995,0.0002</t>
+  </si>
+  <si>
+    <t>0.0392,0.0434,0.0012,0.9497</t>
+  </si>
+  <si>
+    <t>0.0005,0.9994,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.9994,0.0014,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0017,0.9988,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0992,0.9990,0.0001</t>
+  </si>
+  <si>
+    <t>0.0011,0.0001,0.9980,0.0004</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.9991,0.0008</t>
+  </si>
+  <si>
+    <t>0.0001,0.0005,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0257,0.9964,0.0009</t>
+  </si>
+  <si>
+    <t>0.9826,0.0138,0.0025,0.0012</t>
+  </si>
+  <si>
+    <t>0.9979,0.0009,0.0006,0.0007</t>
+  </si>
+  <si>
+    <t>0.9984,0.0009,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0162,0.9995,0.0148</t>
+  </si>
+  <si>
+    <t>0.9989,0.0002,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9976,0.0014,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.9973,0.0025,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9862,0.9901,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0041,0.9983,0.0008</t>
+  </si>
+  <si>
+    <t>0.0057,0.0339,0.9755,0.0029</t>
+  </si>
+  <si>
+    <t>0.0000,0.9984,0.9988,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0041,0.9960,0.0013,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9814,0.0005,0.0239,0.0001</t>
+  </si>
+  <si>
+    <t>0.9392,0.0081,0.0320,0.0004</t>
+  </si>
+  <si>
+    <t>0.0006,0.0019,0.9991,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.6845,0.9833,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.8550,0.9818,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.9989,0.0030,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.6134,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0000,0.0001,0.9997</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0003,0.0002,0.9996</t>
   </si>
   <si>
     <t>0.0002,0.0001,0.0000,0.9999</t>
   </si>
   <si>
-    <t>0.3561,0.0010,0.0001,0.7435</t>
-  </si>
-  <si>
-    <t>0.0659,0.0014,0.0004,0.9699</t>
+    <t>0.0000,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9982,0.0552,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9922,0.9986,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9929,0.9759,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.7107,0.9710,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.9936,0.9936,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9938,0.3716,0.0001</t>
   </si>
   <si>
     <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9998,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9986,0.0001,0.0000,0.0017</t>
+    <t>0.9987,0.0008,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9972,0.0030,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9975,0.0008,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9990,0.0011,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9985,0.0010,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9986,0.0008,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9986,0.0018,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0002,0.0000,0.0001</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0001</t>
   </si>
   <si>
-    <t>0.9995,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0011,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0003,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9454,0.0003,0.0542,0.0002</t>
-  </si>
-  <si>
-    <t>0.0028,0.0018,0.9927,0.0006</t>
-  </si>
-  <si>
-    <t>0.6692,0.0004,0.4660,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.0002,0.9979,0.0002</t>
-  </si>
-  <si>
-    <t>0.9137,0.0006,0.0972,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.9995,0.0019,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0048,0.9940,0.0029,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.9989,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.1226,0.0002,0.8925,0.0004</t>
-  </si>
-  <si>
-    <t>0.0386,0.0069,0.9410,0.0025</t>
-  </si>
-  <si>
-    <t>0.0030,0.0002,0.9966,0.0003</t>
-  </si>
-  <si>
-    <t>0.0564,0.0016,0.9303,0.0004</t>
-  </si>
-  <si>
-    <t>0.0361,0.0000,0.9718,0.0001</t>
-  </si>
-  <si>
-    <t>0.6599,0.0001,0.4217,0.0002</t>
-  </si>
-  <si>
-    <t>0.0009,0.0004,0.9971,0.0028</t>
-  </si>
-  <si>
-    <t>0.4338,0.6712,0.0021,0.0003</t>
-  </si>
-  <si>
-    <t>0.3941,0.5007,0.0230,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0039,0.9997,0.0050</t>
-  </si>
-  <si>
-    <t>0.0020,0.9970,0.0013,0.0002</t>
-  </si>
-  <si>
-    <t>0.9974,0.0004,0.0010,0.0004</t>
-  </si>
-  <si>
-    <t>0.1058,0.0016,0.8980,0.0037</t>
-  </si>
-  <si>
-    <t>0.0233,0.9746,0.0032,0.0002</t>
-  </si>
-  <si>
-    <t>0.0015,0.9969,0.0063,0.0001</t>
-  </si>
-  <si>
-    <t>0.0069,0.9657,0.0301,0.0003</t>
-  </si>
-  <si>
-    <t>0.0117,0.0003,0.9767,0.0020</t>
-  </si>
-  <si>
-    <t>0.0069,0.0039,0.9915,0.0002</t>
-  </si>
-  <si>
-    <t>0.1817,0.0001,0.8060,0.0016</t>
-  </si>
-  <si>
-    <t>0.0010,0.0015,0.9962,0.0004</t>
-  </si>
-  <si>
-    <t>0.0009,0.9982,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0002,0.9990,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.7665,0.0002,0.9718</t>
-  </si>
-  <si>
-    <t>0.0002,0.9998,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
+    <t>0.9995,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9995,0.0006</t>
+  </si>
+  <si>
+    <t>0.0022,0.0041,0.9939,0.0006</t>
+  </si>
+  <si>
+    <t>0.9281,0.0013,0.0172,0.0071</t>
+  </si>
+  <si>
+    <t>0.0088,0.0007,0.9902,0.0003</t>
+  </si>
+  <si>
+    <t>0.0006,0.9993,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0073,0.9889,0.0034,0.0002</t>
+  </si>
+  <si>
+    <t>0.0008,0.9984,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.9991,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.1107,0.9222,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.0598,0.0091,0.8990,0.0021</t>
+  </si>
+  <si>
+    <t>0.9881,0.0001,0.0094,0.0000</t>
+  </si>
+  <si>
+    <t>0.2133,0.2768,0.0595,0.0534</t>
+  </si>
+  <si>
+    <t>0.0473,0.0047,0.9082,0.0052</t>
+  </si>
+  <si>
+    <t>0.0005,0.0581,0.0003,0.9981</t>
   </si>
   <si>
     <t>0.0000,1.0000,0.0003,0.0000</t>
   </si>
   <si>
-    <t>0.0002,0.0091,0.9989,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0045,0.9989,0.0001</t>
-  </si>
-  <si>
-    <t>0.1685,0.0001,0.8738,0.0002</t>
-  </si>
-  <si>
-    <t>0.0014,0.0001,0.9978,0.0009</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0011,0.0143,0.9945,0.0005</t>
-  </si>
-  <si>
-    <t>0.9905,0.0064,0.0020,0.0016</t>
-  </si>
-  <si>
-    <t>0.9984,0.0007,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9983,0.0008,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.0012,0.9997,0.0148</t>
-  </si>
-  <si>
-    <t>0.9991,0.0005,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0006,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9938,0.9953,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0313,0.9973,0.0016</t>
-  </si>
-  <si>
-    <t>0.0008,0.0025,0.9963,0.0013</t>
-  </si>
-  <si>
-    <t>0.0000,0.9940,0.9927,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0063,0.9956,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9998,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.2502,0.0007,0.7865,0.0009</t>
-  </si>
-  <si>
-    <t>0.9812,0.0042,0.0038,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0010,0.9997,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.9687,0.9774,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.6715,0.9894,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9984,0.0059,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9979,0.1168,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0007,0.9997</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
+    <t>0.0001,0.9998,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9988,0.9833,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.9986,0.0016,0.0000</t>
+  </si>
+  <si>
+    <t>0.6135,0.1419,0.0767,0.0003</t>
+  </si>
+  <si>
+    <t>0.7188,0.3110,0.0017,0.0007</t>
+  </si>
+  <si>
+    <t>0.9783,0.0128,0.0002,0.0015</t>
+  </si>
+  <si>
+    <t>0.9988,0.0001,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9989,0.0000,0.0001,0.0017</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9987,0.0009,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9967,0.0001,0.0001,0.0029</t>
+  </si>
+  <si>
+    <t>0.9981,0.0001,0.0002,0.0021</t>
+  </si>
+  <si>
+    <t>0.0001,0.8869,0.9881,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0145,0.9984,0.0000</t>
+  </si>
+  <si>
+    <t>0.0060,0.0018,0.9894,0.0000</t>
+  </si>
+  <si>
+    <t>0.0564,0.0006,0.9554,0.0000</t>
+  </si>
+  <si>
+    <t>0.9935,0.0004,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.0085,0.0005,0.9847,0.0018</t>
+  </si>
+  <si>
+    <t>0.0534,0.0002,0.9514,0.0007</t>
+  </si>
+  <si>
+    <t>0.9649,0.0004,0.0315,0.0001</t>
+  </si>
+  <si>
+    <t>0.0882,0.0001,0.0002,0.9684</t>
   </si>
   <si>
     <t>0.0002,0.0000,0.0000,0.9999</t>
   </si>
   <si>
-    <t>0.0014,0.0002,0.0000,0.9995</t>
-  </si>
-  <si>
-    <t>0.0011,0.0000,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9943,0.9081,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9974,0.9988,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9983,0.9954,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.1725,0.9667,0.0014</t>
-  </si>
-  <si>
-    <t>0.0000,0.9980,0.9852,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.7340,0.9868,0.0001</t>
-  </si>
-  <si>
-    <t>0.9939,0.0073,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9977,0.0013,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9987,0.0005,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9991,0.0003,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0004,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9981,0.0017,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9994,0.0004,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9998,0.0005</t>
-  </si>
-  <si>
-    <t>0.0150,0.0018,0.9838,0.0003</t>
-  </si>
-  <si>
-    <t>0.9444,0.0007,0.0353,0.0008</t>
-  </si>
-  <si>
-    <t>0.0166,0.0004,0.9861,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.9997,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.9992,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0326,0.9658,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.9989,0.0013,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.9994,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.5841,0.5393,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.8854,0.0007,0.0999,0.0006</t>
-  </si>
-  <si>
-    <t>0.0610,0.0002,0.9412,0.0003</t>
-  </si>
-  <si>
-    <t>0.3528,0.0052,0.5561,0.0014</t>
-  </si>
-  <si>
-    <t>0.9436,0.0095,0.0101,0.0006</t>
-  </si>
-  <si>
-    <t>0.0006,0.0020,0.0001,0.9994</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9988,0.8020,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.9988,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.3417,0.4413,0.0736,0.0005</t>
-  </si>
-  <si>
-    <t>0.3140,0.6870,0.0063,0.0005</t>
-  </si>
-  <si>
-    <t>0.9938,0.0047,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9955,0.0010,0.0004,0.0020</t>
-  </si>
-  <si>
-    <t>0.9978,0.0001,0.0001,0.0034</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9971,0.0002,0.0002,0.0036</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.9878,0.9891,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0533,0.9960,0.0000</t>
-  </si>
-  <si>
-    <t>0.0056,0.0013,0.9880,0.0002</t>
-  </si>
-  <si>
-    <t>0.0078,0.0040,0.9850,0.0000</t>
-  </si>
-  <si>
-    <t>0.9943,0.0001,0.0020,0.0000</t>
-  </si>
-  <si>
-    <t>0.9224,0.0006,0.0585,0.0006</t>
-  </si>
-  <si>
-    <t>0.0052,0.0001,0.9940,0.0006</t>
-  </si>
-  <si>
-    <t>0.9806,0.0002,0.0095,0.0002</t>
-  </si>
-  <si>
-    <t>0.0156,0.0003,0.0002,0.9938</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.0000,0.9968,0.9899,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0002,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0070,0.9864,0.0060,0.0006</t>
-  </si>
-  <si>
-    <t>0.9989,0.0001,0.0001,0.0009</t>
-  </si>
-  <si>
-    <t>0.3854,0.5980,0.0047,0.0015</t>
-  </si>
-  <si>
-    <t>0.9961,0.0002,0.0002,0.0046</t>
-  </si>
-  <si>
-    <t>0.8577,0.0002,0.0006,0.1677</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.0005,0.0016,0.9964,0.0132</t>
-  </si>
-  <si>
-    <t>0.8994,0.0000,0.0047,0.0380</t>
-  </si>
-  <si>
-    <t>0.9986,0.0003,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.3159,0.5263,0.0415,0.0009</t>
-  </si>
-  <si>
-    <t>0.9727,0.0116,0.0020,0.0040</t>
-  </si>
-  <si>
-    <t>0.9980,0.0010,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0621,0.7158,0.1416,0.0007</t>
-  </si>
-  <si>
-    <t>0.9735,0.0096,0.0082,0.0001</t>
-  </si>
-  <si>
-    <t>0.9973,0.0010,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9959,0.0006,0.0002,0.0029</t>
-  </si>
-  <si>
-    <t>0.9983,0.0001,0.0000,0.0012</t>
-  </si>
-  <si>
-    <t>0.9990,0.0000,0.0000,0.0011</t>
-  </si>
-  <si>
-    <t>0.9955,0.0001,0.0002,0.0074</t>
-  </si>
-  <si>
-    <t>0.9982,0.0001,0.0001,0.0016</t>
-  </si>
-  <si>
-    <t>0.9978,0.0004,0.0001,0.0010</t>
-  </si>
-  <si>
-    <t>0.9953,0.0010,0.0008,0.0032</t>
-  </si>
-  <si>
-    <t>0.9978,0.0006,0.0003,0.0010</t>
-  </si>
-  <si>
-    <t>0.9703,0.0030,0.0001,0.0062</t>
-  </si>
-  <si>
-    <t>0.8385,0.1565,0.0024,0.0008</t>
-  </si>
-  <si>
-    <t>0.9174,0.1106,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0969,0.9988,0.0003</t>
-  </si>
-  <si>
-    <t>0.9991,0.0013,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9500,0.0065,0.0149,0.0437</t>
-  </si>
-  <si>
-    <t>0.9989,0.0009,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9731,0.0269,0.0004,0.0010</t>
-  </si>
-  <si>
-    <t>0.0000,0.0013,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.8784,0.0879,0.0205,0.0061</t>
-  </si>
-  <si>
-    <t>0.0003,0.0008,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.0058,0.9957,0.0003</t>
-  </si>
-  <si>
-    <t>0.0005,0.0002,0.9989,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0204,0.9991,0.0006</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0017,0.9988,0.0009</t>
-  </si>
-  <si>
-    <t>0.0004,0.0020,0.9979,0.0009</t>
-  </si>
-  <si>
-    <t>0.0188,0.0002,0.9830,0.0001</t>
-  </si>
-  <si>
-    <t>0.0031,0.0013,0.9934,0.0002</t>
-  </si>
-  <si>
-    <t>0.0172,0.0147,0.9673,0.0006</t>
-  </si>
-  <si>
-    <t>0.0476,0.0072,0.9372,0.0001</t>
-  </si>
-  <si>
-    <t>0.4449,0.0004,0.6413,0.0001</t>
-  </si>
-  <si>
-    <t>0.8584,0.0071,0.0725,0.0018</t>
-  </si>
-  <si>
-    <t>0.0050,0.0020,0.9878,0.0013</t>
-  </si>
-  <si>
-    <t>0.4496,0.7255,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.8300,0.3157,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9932,0.0127,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.6990,0.3802,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.1326,0.8998,0.0016,0.0000</t>
-  </si>
-  <si>
-    <t>0.5791,0.0323,0.2398,0.0006</t>
-  </si>
-  <si>
-    <t>0.9992,0.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9642,0.0061,0.0024,0.0023</t>
-  </si>
-  <si>
-    <t>0.9867,0.0006,0.0042,0.0001</t>
-  </si>
-  <si>
-    <t>0.0107,0.0053,0.9722,0.0141</t>
-  </si>
-  <si>
-    <t>0.0036,0.0027,0.9893,0.0034</t>
-  </si>
-  <si>
-    <t>0.0026,0.0051,0.9879,0.0042</t>
-  </si>
-  <si>
-    <t>0.0441,0.0188,0.9399,0.0002</t>
-  </si>
-  <si>
-    <t>0.0015,0.0014,0.9972,0.0001</t>
-  </si>
-  <si>
-    <t>0.0009,0.0067,0.9951,0.0004</t>
-  </si>
-  <si>
-    <t>0.9938,0.0038,0.0014,0.0019</t>
-  </si>
-  <si>
-    <t>0.9984,0.0001,0.0001,0.0016</t>
-  </si>
-  <si>
-    <t>0.9983,0.0011,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9989,0.0006,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9959,0.0016,0.0009,0.0026</t>
-  </si>
-  <si>
-    <t>0.9963,0.0028,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9974,0.0003,0.0001,0.0017</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0006,0.9999,0.0015</t>
-  </si>
-  <si>
-    <t>0.0136,0.0129,0.9638,0.0029</t>
-  </si>
-  <si>
-    <t>0.9668,0.0014,0.0071,0.0081</t>
-  </si>
-  <si>
-    <t>0.0146,0.0000,0.9917,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0007,0.9989,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.0106,0.9976,0.0007</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0350,0.0002,0.9718,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0005,0.9992,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.0041,0.9981,0.0009</t>
-  </si>
-  <si>
-    <t>0.0557,0.0014,0.9153,0.0053</t>
-  </si>
-  <si>
-    <t>0.9895,0.0000,0.0074,0.0000</t>
-  </si>
-  <si>
-    <t>0.9019,0.0004,0.0956,0.0005</t>
-  </si>
-  <si>
-    <t>0.9985,0.0016,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0008,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9954,0.0039,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.9989,0.0001,0.0000,0.0006</t>
-  </si>
-  <si>
-    <t>0.9976,0.0027,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.0022,0.9977,0.0002</t>
-  </si>
-  <si>
-    <t>0.0084,0.0010,0.9899,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0108,0.9992,0.0001</t>
-  </si>
-  <si>
-    <t>0.0149,0.0361,0.9489,0.0008</t>
-  </si>
-  <si>
-    <t>0.0667,0.0000,0.9571,0.0000</t>
-  </si>
-  <si>
-    <t>0.0057,0.0009,0.9824,0.0179</t>
-  </si>
-  <si>
-    <t>0.0031,0.0003,0.9943,0.0004</t>
-  </si>
-  <si>
-    <t>0.0139,0.0087,0.9660,0.0062</t>
-  </si>
-  <si>
-    <t>0.8105,0.0000,0.0005,0.2379</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0080,0.0001,0.0000,0.9980</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.9926,0.0001,0.0001,0.0017</t>
+    <t>0.0000,0.9993,0.9745,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0053,0.9916,0.0017,0.0003</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.0384,0.9608,0.0022,0.0003</t>
+  </si>
+  <si>
+    <t>0.9981,0.0002,0.0006,0.0012</t>
+  </si>
+  <si>
+    <t>0.3523,0.0001,0.0002,0.8717</t>
+  </si>
+  <si>
+    <t>0.0003,0.0053,0.9974,0.0109</t>
+  </si>
+  <si>
+    <t>0.8441,0.0000,0.0038,0.0671</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.2622,0.7991,0.0020,0.0005</t>
+  </si>
+  <si>
+    <t>0.9741,0.0226,0.0006,0.0007</t>
+  </si>
+  <si>
+    <t>0.9832,0.0076,0.0050,0.0002</t>
+  </si>
+  <si>
+    <t>0.0796,0.0977,0.5760,0.0011</t>
+  </si>
+  <si>
+    <t>0.9899,0.0040,0.0020,0.0000</t>
+  </si>
+  <si>
+    <t>0.9982,0.0008,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9947,0.0026,0.0004,0.0013</t>
+  </si>
+  <si>
+    <t>0.9995,0.0003,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0000,0.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.9885,0.0002,0.0006,0.0153</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.9975,0.0010,0.0004,0.0010</t>
+  </si>
+  <si>
+    <t>0.9969,0.0009,0.0009,0.0020</t>
+  </si>
+  <si>
+    <t>0.9989,0.0001,0.0001,0.0010</t>
+  </si>
+  <si>
+    <t>0.8305,0.0170,0.0001,0.0150</t>
+  </si>
+  <si>
+    <t>0.7359,0.2613,0.0052,0.0008</t>
+  </si>
+  <si>
+    <t>0.9339,0.0892,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.0118,0.9978,0.0009</t>
+  </si>
+  <si>
+    <t>0.9989,0.0014,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9625,0.0012,0.0002,0.0335</t>
+  </si>
+  <si>
+    <t>0.9994,0.0003,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9428,0.0570,0.0013,0.0017</t>
+  </si>
+  <si>
+    <t>0.0000,0.0011,1.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9616,0.0264,0.0074,0.0089</t>
+  </si>
+  <si>
+    <t>0.0001,0.0014,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0618,0.9973,0.0008</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9995,0.0005</t>
+  </si>
+  <si>
+    <t>0.0014,0.0697,0.9907,0.0007</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0006,0.9997,0.0007</t>
+  </si>
+  <si>
+    <t>0.0009,0.0010,0.9967,0.0014</t>
+  </si>
+  <si>
+    <t>0.0394,0.0005,0.9594,0.0007</t>
+  </si>
+  <si>
+    <t>0.1616,0.0054,0.8058,0.0006</t>
+  </si>
+  <si>
+    <t>0.0675,0.0042,0.9342,0.0000</t>
+  </si>
+  <si>
+    <t>0.0067,0.5275,0.8291,0.0002</t>
+  </si>
+  <si>
+    <t>0.3996,0.0010,0.6589,0.0001</t>
+  </si>
+  <si>
+    <t>0.5259,0.0017,0.4218,0.0012</t>
+  </si>
+  <si>
+    <t>0.1145,0.0086,0.8101,0.0021</t>
+  </si>
+  <si>
+    <t>0.2827,0.8090,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.1190,0.9366,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9959,0.0091,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.2383,0.8421,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0172,0.9816,0.0025,0.0001</t>
+  </si>
+  <si>
+    <t>0.8501,0.0301,0.0545,0.0005</t>
+  </si>
+  <si>
+    <t>0.9939,0.0000,0.0070,0.0000</t>
+  </si>
+  <si>
+    <t>0.6618,0.1258,0.0056,0.0394</t>
+  </si>
+  <si>
+    <t>0.5093,0.0084,0.3627,0.0020</t>
+  </si>
+  <si>
+    <t>0.0059,0.0131,0.9788,0.0068</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9994,0.0006</t>
+  </si>
+  <si>
+    <t>0.0029,0.0662,0.9793,0.0013</t>
+  </si>
+  <si>
+    <t>0.0547,0.0184,0.9254,0.0005</t>
+  </si>
+  <si>
+    <t>0.0428,0.0002,0.9646,0.0001</t>
+  </si>
+  <si>
+    <t>0.0347,0.1140,0.7425,0.0022</t>
+  </si>
+  <si>
+    <t>0.9982,0.0005,0.0002,0.0011</t>
+  </si>
+  <si>
+    <t>0.9946,0.0024,0.0007,0.0018</t>
+  </si>
+  <si>
+    <t>0.9954,0.0007,0.0002,0.0027</t>
+  </si>
+  <si>
+    <t>0.9927,0.0057,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.9961,0.0025,0.0004,0.0009</t>
+  </si>
+  <si>
+    <t>0.9982,0.0015,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9983,0.0001,0.0001,0.0016</t>
+  </si>
+  <si>
+    <t>0.9985,0.0000,0.0000,0.0033</t>
+  </si>
+  <si>
+    <t>0.0000,0.0007,0.9999,0.0023</t>
+  </si>
+  <si>
+    <t>0.0225,0.0752,0.8842,0.0078</t>
+  </si>
+  <si>
+    <t>0.9323,0.0019,0.0222,0.0074</t>
+  </si>
+  <si>
+    <t>0.0025,0.0001,0.9981,0.0000</t>
+  </si>
+  <si>
+    <t>0.0716,0.0010,0.9424,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0319,0.9973,0.0009</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0060,0.0010,0.9908,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0015,0.9977,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0025,0.9981,0.0009</t>
+  </si>
+  <si>
+    <t>0.6274,0.0013,0.3355,0.0010</t>
+  </si>
+  <si>
+    <t>0.5001,0.0004,0.4593,0.0019</t>
+  </si>
+  <si>
+    <t>0.9934,0.0001,0.0014,0.0002</t>
+  </si>
+  <si>
+    <t>0.9993,0.0007,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0007,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9980,0.0010,0.0004,0.0007</t>
+  </si>
+  <si>
+    <t>0.9975,0.0004,0.0001,0.0011</t>
+  </si>
+  <si>
+    <t>0.9978,0.0016,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9993,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0007,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0061,0.0070,0.9855,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0007,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0023,0.9988,0.0003</t>
+  </si>
+  <si>
+    <t>0.0536,0.0047,0.9321,0.0002</t>
+  </si>
+  <si>
+    <t>0.2556,0.0001,0.8061,0.0001</t>
+  </si>
+  <si>
+    <t>0.0011,0.0005,0.9939,0.0215</t>
+  </si>
+  <si>
+    <t>0.0045,0.0030,0.9876,0.0015</t>
+  </si>
+  <si>
+    <t>0.0135,0.0014,0.9735,0.0045</t>
+  </si>
+  <si>
+    <t>0.6633,0.0003,0.0070,0.2418</t>
+  </si>
+  <si>
+    <t>0.0000,0.0013,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0780,0.0003,0.0002,0.9615</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.8538,0.0002,0.0000,0.0973</t>
   </si>
 </sst>
 </file>
@@ -1926,7 +1920,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1940,7 +1934,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1951,10 +1945,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1968,7 +1962,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1982,7 +1976,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1996,7 +1990,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2010,7 +2004,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2024,7 +2018,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2038,7 +2032,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2052,7 +2046,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2066,7 +2060,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2091,7 +2085,7 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D14" t="s">
         <v>277</v>
@@ -2231,7 +2225,7 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
         <v>287</v>
@@ -2245,7 +2239,7 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
         <v>288</v>
@@ -2329,7 +2323,7 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
         <v>294</v>
@@ -2343,7 +2337,7 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D32" t="s">
         <v>295</v>
@@ -2539,7 +2533,7 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
         <v>309</v>
@@ -2875,7 +2869,7 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D70" t="s">
         <v>333</v>
@@ -2959,7 +2953,7 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
         <v>339</v>
@@ -3057,7 +3051,7 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D83" t="s">
         <v>346</v>
@@ -3099,7 +3093,7 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
         <v>349</v>
@@ -3127,7 +3121,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
         <v>351</v>
@@ -3144,7 +3138,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>269</v>
+        <v>352</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3158,7 +3152,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>325</v>
+        <v>353</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3172,7 +3166,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3186,7 +3180,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3200,7 +3194,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3214,7 +3208,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3228,7 +3222,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3242,7 +3236,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3256,7 +3250,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3270,7 +3264,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3284,7 +3278,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3298,7 +3292,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>269</v>
+        <v>352</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3312,7 +3306,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3326,7 +3320,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3340,7 +3334,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3354,7 +3348,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3368,7 +3362,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3382,7 +3376,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3396,7 +3390,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3410,7 +3404,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3424,7 +3418,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3438,7 +3432,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3452,7 +3446,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3466,7 +3460,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3480,7 +3474,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3494,7 +3488,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>373</v>
+        <v>332</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3508,7 +3502,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3519,10 +3513,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D116" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3533,10 +3527,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3547,10 +3541,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D118" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3561,10 +3555,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3578,7 +3572,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3592,7 +3586,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>312</v>
+        <v>286</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3606,7 +3600,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3620,7 +3614,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3634,7 +3628,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3648,7 +3642,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3662,7 +3656,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3673,10 +3667,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3690,7 +3684,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3704,7 +3698,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3718,7 +3712,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3732,7 +3726,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3746,7 +3740,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3760,7 +3754,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>390</v>
+        <v>273</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3774,7 +3768,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3788,7 +3782,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3802,7 +3796,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3816,7 +3810,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3830,7 +3824,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3844,7 +3838,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3858,7 +3852,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3869,10 +3863,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3886,7 +3880,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3900,7 +3894,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3914,7 +3908,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3942,7 +3936,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3956,7 +3950,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3970,7 +3964,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3984,7 +3978,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3998,7 +3992,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4012,7 +4006,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4026,7 +4020,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4040,7 +4034,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4051,10 +4045,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4068,7 +4062,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>410</v>
+        <v>273</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4082,7 +4076,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4096,7 +4090,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4110,7 +4104,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4124,7 +4118,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4138,7 +4132,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4152,7 +4146,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4163,10 +4157,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D162" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4180,7 +4174,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4194,7 +4188,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4208,7 +4202,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4222,7 +4216,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4236,7 +4230,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4250,7 +4244,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4264,7 +4258,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4278,7 +4272,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4292,7 +4286,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4306,7 +4300,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4320,7 +4314,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4334,7 +4328,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4348,7 +4342,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4362,7 +4356,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4376,7 +4370,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4390,7 +4384,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4404,7 +4398,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4418,7 +4412,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4432,7 +4426,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4446,7 +4440,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4460,7 +4454,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4474,7 +4468,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4488,7 +4482,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4502,7 +4496,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4516,7 +4510,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4530,7 +4524,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4544,7 +4538,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4558,7 +4552,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4572,7 +4566,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4586,7 +4580,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4600,7 +4594,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4611,10 +4605,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D194" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4628,7 +4622,7 @@
         <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4642,7 +4636,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4656,7 +4650,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4670,7 +4664,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4681,10 +4675,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4698,7 +4692,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4709,10 +4703,10 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4726,7 +4720,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4740,7 +4734,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4754,7 +4748,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4768,7 +4762,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4782,7 +4776,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4796,7 +4790,7 @@
         <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4810,7 +4804,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4824,7 +4818,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4838,7 +4832,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4852,7 +4846,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4866,7 +4860,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4880,7 +4874,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4894,7 +4888,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4908,7 +4902,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4922,7 +4916,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4936,7 +4930,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4950,7 +4944,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4964,7 +4958,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4978,7 +4972,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4992,7 +4986,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5006,7 +5000,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5020,7 +5014,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5034,7 +5028,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5048,7 +5042,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5062,7 +5056,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5076,7 +5070,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5090,7 +5084,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5104,7 +5098,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5118,7 +5112,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5132,7 +5126,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5143,10 +5137,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5160,7 +5154,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5174,7 +5168,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5188,7 +5182,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5202,7 +5196,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5216,7 +5210,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>492</v>
+        <v>360</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5230,7 +5224,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5244,7 +5238,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5258,7 +5252,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>325</v>
+        <v>491</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5272,7 +5266,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5286,7 +5280,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5300,7 +5294,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5314,7 +5308,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5328,7 +5322,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5342,7 +5336,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5356,7 +5350,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5370,7 +5364,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5384,7 +5378,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5398,7 +5392,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5412,7 +5406,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5426,7 +5420,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5440,7 +5434,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5454,7 +5448,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5468,7 +5462,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>341</v>
+        <v>505</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5482,7 +5476,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
   </sheetData>
